--- a/assets/constructions/examples/ctd_tko_face_fullround.xlsx
+++ b/assets/constructions/examples/ctd_tko_face_fullround.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,11 +604,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V14FEGR100T500RVBX</t>
+          <t>V14FGR150T300RVBX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -638,18 +663,18 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
         <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -661,16 +686,16 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>10.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -691,12 +716,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -719,39 +744,58 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>2463.82</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V14FGR050T150RVBX</t>
+          <t>R114.1410.05 TN35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>HORN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mini-V</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>V14</t>
+          <t>B114</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>HORN</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -770,15 +814,17 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>9</v>
       </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="Q3" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -794,11 +840,15 @@
           <t>R</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.03</v>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>VARGUS_V14</t>
+          <t>HORN_114R</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -808,12 +858,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>TN35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -835,14 +885,25 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>2014-2015 / Carbide Grooving Tools Catalog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V14FGR150T300RVBX</t>
+          <t>V14FEGR125T500RVBX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -872,18 +933,18 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -895,16 +956,16 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -953,6 +1014,25 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>2958.43</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
@@ -1072,11 +1152,30 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>2463.82</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V14FEGR125T500RVBX</t>
+          <t>V14FGR050T150RVBX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1106,18 +1205,18 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
         <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -1129,16 +1228,16 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>10.7</v>
+        <v>7.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1159,12 +1258,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1187,6 +1286,25 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>2463.82</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
